--- a/KUBERNETES/Kubernetes_liste_des_commandes.xlsx
+++ b/KUBERNETES/Kubernetes_liste_des_commandes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a5f61b3e4cd8107/Inès_perso/M2i_administraeur_CLOUD.0.0/Cours_Python_M2i/KUBERNETES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2412" documentId="8_{4309FA21-DA46-4726-B3AF-5F415FC36ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D317B7D-6E86-4244-8152-AE2A9DCDA1BF}"/>
+  <xr:revisionPtr revIDLastSave="2416" documentId="8_{4309FA21-DA46-4726-B3AF-5F415FC36ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57BEE1FD-23A6-4850-9C2B-81B76277876E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8D2D9E53-07E4-4E8B-82A4-55704ED06D6A}"/>
+    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" xr2:uid="{8D2D9E53-07E4-4E8B-82A4-55704ED06D6A}"/>
   </bookViews>
   <sheets>
     <sheet name="Listes_des_commandes" sheetId="1" r:id="rId1"/>
@@ -382,9 +382,6 @@
     <t>Créer à partir d'un fichier YAML</t>
   </si>
   <si>
-    <t>kubectl create -f deployment.yaml</t>
-  </si>
-  <si>
     <t>Créer un service</t>
   </si>
   <si>
@@ -4788,10 +4785,26 @@
     <t>Cette commande crée un Service nommé storefront à partir du Deployment</t>
   </si>
   <si>
-    <t>²</t>
-  </si>
-  <si>
     <t>kubectl create namespace &lt;nom_donné&gt;</t>
+  </si>
+  <si>
+    <t>apiVersion: networking.k8s.io/v1
+kind: Ingress
+metadata:
+  name: webapp-ingress
+  annotations:
+    kubernetes.io/ingress.class: nginx
+spec:
+  rules:
+  - host: webapp.example.com
+    http:
+      paths:
+      - path: /
+        pathType: Prefix
+        backe</t>
+  </si>
+  <si>
+    <t>A trouver</t>
   </si>
 </sst>
 </file>
@@ -5453,33 +5466,33 @@
     </row>
     <row r="2" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="B2" s="27" t="s">
         <v>208</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="C2" s="27" t="s">
         <v>209</v>
-      </c>
-      <c r="C2" s="27" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="38"/>
       <c r="B4" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="60" x14ac:dyDescent="0.25">
@@ -5490,27 +5503,27 @@
         <v>12</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="34"/>
       <c r="B7" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -5521,16 +5534,16 @@
         <v>3</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="43"/>
       <c r="B9" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>172</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -5598,13 +5611,13 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="42" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>185</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -5647,7 +5660,7 @@
         <v>9</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="90" x14ac:dyDescent="0.25">
@@ -5658,7 +5671,7 @@
         <v>7</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -5697,12 +5710,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="210" x14ac:dyDescent="0.25">
       <c r="A28" s="42" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>82</v>
+        <v>623</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>81</v>
@@ -5711,57 +5724,57 @@
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="42"/>
       <c r="B29" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="42"/>
       <c r="B30" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="42"/>
       <c r="B31" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="39" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>63</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="40"/>
       <c r="B33" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="C33" s="9" t="s">
         <v>190</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="40"/>
       <c r="B34" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -5770,16 +5783,16 @@
         <v>64</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="40"/>
       <c r="B36" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="60" x14ac:dyDescent="0.25">
@@ -5788,16 +5801,16 @@
         <v>20</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="40"/>
       <c r="B38" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -5810,28 +5823,28 @@
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="40"/>
       <c r="B40" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="40"/>
       <c r="B41" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="40"/>
       <c r="B42" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -5858,81 +5871,81 @@
         <v>19</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A46" s="40"/>
       <c r="B46" s="9" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C46" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="210" x14ac:dyDescent="0.25">
       <c r="A47" s="40"/>
       <c r="B47" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="C47" s="30" t="s">
         <v>589</v>
-      </c>
-      <c r="C47" s="30" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="40"/>
       <c r="B48" s="9" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C48" s="30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="40"/>
       <c r="B49" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="C49" s="30" t="s">
         <v>592</v>
-      </c>
-      <c r="C49" s="30" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="41"/>
       <c r="B50" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A51" s="42" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>596</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="42"/>
       <c r="B52" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="42"/>
       <c r="B53" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -5941,7 +5954,7 @@
         <v>71</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -5950,83 +5963,83 @@
         <v>18</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A56" s="42"/>
       <c r="B56" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="43" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="43"/>
       <c r="B58" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C58" s="9" t="s">
         <v>101</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="43"/>
       <c r="B59" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C59" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="43"/>
       <c r="B60" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A61" s="42" t="s">
+        <v>199</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="C61" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="42"/>
       <c r="B62" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A63" s="42"/>
       <c r="B63" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -6050,10 +6063,10 @@
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="42"/>
       <c r="B66" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="60" x14ac:dyDescent="0.25">
@@ -6062,1878 +6075,1878 @@
         <v>50</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="43" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B68" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C68" s="9" t="s">
         <v>112</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="43"/>
       <c r="B69" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C69" s="9" t="s">
         <v>114</v>
-      </c>
-      <c r="C69" s="9" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="42"/>
       <c r="B71" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="43" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B72" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C72" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="43"/>
       <c r="B73" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C73" s="9" t="s">
         <v>126</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="43"/>
       <c r="B74" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C74" s="9" t="s">
         <v>128</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="43"/>
       <c r="B75" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="C75" s="9" t="s">
         <v>615</v>
-      </c>
-      <c r="C75" s="9" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="43"/>
       <c r="B76" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C76" s="9" t="s">
         <v>130</v>
-      </c>
-      <c r="C76" s="9" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="42" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B77" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="42"/>
       <c r="B78" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="42"/>
       <c r="B79" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>617</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="42"/>
       <c r="B80" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="43" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="43"/>
       <c r="B82" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="C83" s="1"/>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="39" t="s">
+        <v>214</v>
+      </c>
+      <c r="B84" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="B84" s="9" t="s">
-        <v>216</v>
-      </c>
       <c r="C84" s="44" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="41"/>
       <c r="B85" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C85" s="45"/>
     </row>
     <row r="86" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="36" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B86" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C86" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="37"/>
       <c r="B87" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="37"/>
       <c r="B88" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C88" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A89" s="38"/>
       <c r="B89" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A90" s="14" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B90" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="C90" s="15" t="s">
         <v>221</v>
-      </c>
-      <c r="C90" s="15" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="36" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B91" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C91" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="38"/>
       <c r="B92" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="39" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B93" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C93" s="15" t="s">
         <v>229</v>
-      </c>
-      <c r="C93" s="15" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="41"/>
       <c r="B94" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C95" s="6" t="s">
         <v>235</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="38"/>
       <c r="B96" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C96" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="39" t="s">
+        <v>238</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="C97" s="15" t="s">
         <v>239</v>
-      </c>
-      <c r="B97" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="C97" s="15" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="40"/>
       <c r="B98" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="41"/>
       <c r="B99" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C100" s="6" t="s">
         <v>246</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="270" x14ac:dyDescent="0.25">
       <c r="A101" s="34"/>
       <c r="B101" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="39" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B102" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="C102" s="23" t="s">
         <v>251</v>
-      </c>
-      <c r="C102" s="23" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="40"/>
       <c r="B103" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="40"/>
       <c r="B104" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="40"/>
       <c r="B105" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C105" s="15" t="s">
         <v>257</v>
-      </c>
-      <c r="C105" s="15" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="41"/>
       <c r="B106" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="36" t="s">
+        <v>261</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="C107" s="6" t="s">
         <v>263</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="37"/>
       <c r="B108" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="38"/>
       <c r="B109" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C109" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="39" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B110" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="C110" s="15" t="s">
         <v>269</v>
-      </c>
-      <c r="C110" s="15" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="40"/>
       <c r="B111" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="40"/>
       <c r="B112" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="C112" s="15" t="s">
         <v>273</v>
-      </c>
-      <c r="C112" s="15" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="40"/>
       <c r="B113" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="C113" s="15" t="s">
         <v>275</v>
-      </c>
-      <c r="C113" s="15" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="41"/>
       <c r="B114" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="36" t="s">
+        <v>279</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C115" s="6" t="s">
         <v>280</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C115" s="6" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="38"/>
       <c r="B116" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A117" s="39" t="s">
+        <v>284</v>
+      </c>
+      <c r="B117" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="C117" s="15" t="s">
         <v>285</v>
-      </c>
-      <c r="B117" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="C117" s="15" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="40"/>
       <c r="B118" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A119" s="41"/>
       <c r="B119" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C120" s="6" t="s">
         <v>292</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="C120" s="6" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="37"/>
       <c r="B121" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C121" s="19" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="37"/>
       <c r="B122" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C122" s="19" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="38"/>
       <c r="B123" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="39" t="s">
+        <v>300</v>
+      </c>
+      <c r="B124" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C124" s="23" t="s">
         <v>301</v>
-      </c>
-      <c r="B124" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="C124" s="23" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="41"/>
       <c r="B125" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="36" t="s">
+        <v>305</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C126" s="19" t="s">
         <v>306</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C126" s="19" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="37"/>
       <c r="B127" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C127" s="19" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="38"/>
       <c r="B128" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C128" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="B129" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="C129" s="23" t="s">
         <v>312</v>
-      </c>
-      <c r="B129" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="C129" s="23" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A130" s="41"/>
       <c r="B130" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C130" s="23"/>
     </row>
     <row r="131" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A131" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="B131" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="C131" s="19" t="s">
         <v>316</v>
-      </c>
-      <c r="B131" s="17" t="s">
-        <v>318</v>
-      </c>
-      <c r="C131" s="19" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="39" t="s">
+        <v>318</v>
+      </c>
+      <c r="B132" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="B132" s="9" t="s">
+      <c r="C132" s="23" t="s">
         <v>320</v>
-      </c>
-      <c r="C132" s="23" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="40"/>
       <c r="B133" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C133" s="23" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="41"/>
       <c r="B134" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C134" s="24" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="36" t="s">
+        <v>325</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C135" s="19" t="s">
         <v>326</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C135" s="19" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="38"/>
       <c r="B136" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C136" s="20" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B137" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="C137" s="9" t="s">
         <v>331</v>
-      </c>
-      <c r="C137" s="9" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="41"/>
       <c r="B138" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C138" s="23" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="36" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C139" s="19" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="38"/>
       <c r="B140" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C140" s="19" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A141" s="39" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C141" s="23" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="41"/>
       <c r="B142" s="25" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C142" s="23" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A143" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C143" s="19" t="s">
         <v>345</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="C143" s="19" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="39" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B144" s="25" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C144" s="23" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="40"/>
       <c r="B145" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C145" s="23" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="41"/>
       <c r="B146" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C146" s="23" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="36" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C147" s="19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="37"/>
       <c r="B148" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C148" s="19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="37"/>
       <c r="B149" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C149" s="19" t="s">
         <v>157</v>
-      </c>
-      <c r="C149" s="19" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="37"/>
       <c r="B150" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C150" s="19" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="38"/>
       <c r="B151" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C151" s="19"/>
     </row>
     <row r="152" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="39" t="s">
+        <v>358</v>
+      </c>
+      <c r="B152" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="C152" s="23" t="s">
         <v>359</v>
-      </c>
-      <c r="B152" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="C152" s="23" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="40"/>
       <c r="B153" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="C153" s="29" t="s">
         <v>362</v>
-      </c>
-      <c r="C153" s="29" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="40"/>
       <c r="B154" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C154" s="23" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="40"/>
       <c r="B155" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C155" s="23" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="40"/>
       <c r="B156" s="9" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C156" s="23" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="40"/>
       <c r="B157" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C157" s="23" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A158" s="41"/>
       <c r="B158" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C158" s="23" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="48" t="s">
+        <v>373</v>
+      </c>
+      <c r="B159" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="C159" s="21" t="s">
         <v>374</v>
-      </c>
-      <c r="B159" s="21" t="s">
-        <v>387</v>
-      </c>
-      <c r="C159" s="21" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="49"/>
       <c r="B160" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C160" s="21" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="49"/>
       <c r="B161" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C161" s="21" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="49"/>
       <c r="B162" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C162" s="21" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="49"/>
       <c r="B163" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C163" s="19" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="49"/>
       <c r="B164" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C164" s="19" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="49"/>
       <c r="B165" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C165" s="20" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="49"/>
       <c r="B166" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C166" s="20" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="50"/>
       <c r="B167" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C167" s="19" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="39" t="s">
+        <v>387</v>
+      </c>
+      <c r="B168" s="25" t="s">
+        <v>389</v>
+      </c>
+      <c r="C168" s="23" t="s">
         <v>388</v>
-      </c>
-      <c r="B168" s="25" t="s">
-        <v>390</v>
-      </c>
-      <c r="C168" s="23" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="40"/>
       <c r="B169" s="9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C169" s="23" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="40"/>
       <c r="B170" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C170" s="23" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="41"/>
       <c r="B171" s="9" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C171" s="23" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="36" t="s">
+        <v>394</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C172" s="19" t="s">
         <v>395</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="C172" s="19" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="37"/>
       <c r="B173" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C173" s="19" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A174" s="37"/>
       <c r="B174" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C174" s="19" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="38"/>
       <c r="B175" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C175" s="19" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="39" t="s">
+        <v>403</v>
+      </c>
+      <c r="B176" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="C176" s="23" t="s">
         <v>404</v>
-      </c>
-      <c r="B176" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="C176" s="23" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A177" s="40"/>
       <c r="B177" s="9" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C177" s="23" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="41"/>
       <c r="B178" s="9" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C178" s="23" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C179" s="19" t="s">
         <v>410</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="C179" s="19" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A180" s="37"/>
       <c r="B180" s="8" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C180" s="19" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="37"/>
       <c r="B181" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C181" s="19" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A182" s="38"/>
       <c r="B182" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C182" s="19" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="39" t="s">
+        <v>418</v>
+      </c>
+      <c r="B183" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="C183" s="23" t="s">
         <v>419</v>
-      </c>
-      <c r="B183" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="C183" s="23" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A184" s="40"/>
       <c r="B184" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C184" s="23" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="40"/>
       <c r="B185" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C185" s="29" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A186" s="41"/>
       <c r="B186" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C186" s="23" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A187" s="36" t="s">
+        <v>427</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C187" s="19" t="s">
         <v>428</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C187" s="19" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A188" s="37"/>
       <c r="B188" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C188" s="19" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A189" s="38"/>
       <c r="B189" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C189" s="19" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="39" t="s">
+        <v>434</v>
+      </c>
+      <c r="B190" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="C190" s="23" t="s">
         <v>435</v>
-      </c>
-      <c r="B190" s="9" t="s">
-        <v>437</v>
-      </c>
-      <c r="C190" s="23" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A191" s="40"/>
       <c r="B191" s="9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C191" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="41"/>
       <c r="B192" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C192" s="23" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="36" t="s">
+        <v>441</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C193" s="19" t="s">
         <v>442</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="C193" s="19" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="37"/>
       <c r="B194" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C194" s="19" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="37"/>
       <c r="B195" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C195" s="19" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A196" s="38"/>
       <c r="B196" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C196" s="19" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="39" t="s">
+        <v>450</v>
+      </c>
+      <c r="B197" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="C197" s="23" t="s">
         <v>451</v>
-      </c>
-      <c r="B197" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="C197" s="23" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="40"/>
       <c r="B198" s="9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C198" s="23" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="40"/>
       <c r="B199" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C199" s="23" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="40"/>
       <c r="B200" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C200" s="23" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="41"/>
       <c r="B201" s="9" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C201" s="23" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="36" t="s">
+        <v>458</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C202" s="22" t="s">
         <v>459</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="C202" s="22" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="37"/>
       <c r="B203" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C203" s="22" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="37"/>
       <c r="B204" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C204" s="22" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="38"/>
       <c r="B205" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C205" s="22" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="270" x14ac:dyDescent="0.25">
       <c r="A206" s="14" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B206" s="9" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C206" s="23"/>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="36" t="s">
+        <v>468</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C207" s="19" t="s">
         <v>469</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="C207" s="19" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="37"/>
       <c r="B208" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C208" s="19" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="37"/>
       <c r="B209" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C209" s="19" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="37"/>
       <c r="B210" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C210" s="19" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="37"/>
       <c r="B211" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C211" s="19" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="37"/>
       <c r="B212" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C212" s="19" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="37"/>
       <c r="B213" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C213" s="19" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="38"/>
       <c r="B214" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C214" s="19" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="39" t="s">
+        <v>481</v>
+      </c>
+      <c r="B215" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="C215" s="23" t="s">
         <v>482</v>
-      </c>
-      <c r="B215" s="9" t="s">
-        <v>484</v>
-      </c>
-      <c r="C215" s="23" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="40"/>
       <c r="B216" s="9" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C216" s="23" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="40"/>
       <c r="B217" s="9" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C217" s="23" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="41"/>
       <c r="B218" s="9" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C218" s="23" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="36" t="s">
+        <v>526</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C219" s="22" t="s">
         <v>527</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="C219" s="22" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="37"/>
       <c r="B220" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C220" s="28" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A221" s="38"/>
       <c r="B221" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C221" s="22" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="39" t="s">
+        <v>533</v>
+      </c>
+      <c r="B222" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="C222" s="23" t="s">
         <v>534</v>
-      </c>
-      <c r="B222" s="9" t="s">
-        <v>536</v>
-      </c>
-      <c r="C222" s="23" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="40"/>
       <c r="B223" s="9" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C223" s="23" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="40"/>
       <c r="B224" s="9" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C224" s="23" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="41"/>
       <c r="B225" s="9" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C225" s="23" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="36" t="s">
+        <v>542</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>544</v>
-      </c>
       <c r="C226" s="22" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="37"/>
       <c r="B227" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C227" s="22" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="38"/>
       <c r="B228" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C228" s="22" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="39" t="s">
+        <v>548</v>
+      </c>
+      <c r="B229" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="C229" s="23" t="s">
         <v>549</v>
-      </c>
-      <c r="B229" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="C229" s="23" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A230" s="40"/>
       <c r="B230" s="9" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C230" s="23" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="41"/>
       <c r="B231" s="9" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C231" s="23" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="36" t="s">
+        <v>489</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="B232" s="1" t="s">
+      <c r="C232" s="19" t="s">
         <v>491</v>
-      </c>
-      <c r="C232" s="19" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="37"/>
       <c r="B233" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C233" s="19" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="37"/>
       <c r="B234" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C234" s="19" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="38"/>
       <c r="B235" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C235" s="19" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A236" s="14" t="s">
+        <v>497</v>
+      </c>
+      <c r="B236" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="B236" s="9" t="s">
+      <c r="C236" s="23" t="s">
         <v>499</v>
-      </c>
-      <c r="C236" s="23" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="36" t="s">
+        <v>500</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C237" s="19" t="s">
         <v>501</v>
-      </c>
-      <c r="B237" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="C237" s="19" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A238" s="37"/>
       <c r="B238" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C238" s="19" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A239" s="38"/>
       <c r="B239" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C239" s="19" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A240" s="39" t="s">
+        <v>507</v>
+      </c>
+      <c r="B240" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="C240" s="23" t="s">
         <v>508</v>
-      </c>
-      <c r="B240" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="C240" s="23" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A241" s="41"/>
       <c r="B241" s="9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C241" s="23" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="36" t="s">
+        <v>512</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C242" s="19" t="s">
         <v>513</v>
-      </c>
-      <c r="B242" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="C242" s="19" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="38"/>
       <c r="B243" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C243" s="19" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="39" t="s">
+        <v>517</v>
+      </c>
+      <c r="B244" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="C244" s="23" t="s">
         <v>518</v>
-      </c>
-      <c r="B244" s="9" t="s">
-        <v>520</v>
-      </c>
-      <c r="C244" s="23" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="40"/>
       <c r="B245" s="9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C245" s="23" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="40"/>
       <c r="B246" s="9" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C246" s="23" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="41"/>
       <c r="B247" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C247" s="23" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="36" t="s">
+        <v>555</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="C248" s="19" t="s">
         <v>556</v>
-      </c>
-      <c r="B248" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="C248" s="19" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A249" s="37"/>
       <c r="B249" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C249" s="19" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="38"/>
       <c r="B250" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C250" s="19" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="39" t="s">
+        <v>562</v>
+      </c>
+      <c r="B251" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="C251" s="23" t="s">
         <v>563</v>
-      </c>
-      <c r="B251" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="C251" s="23" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="40"/>
       <c r="B252" s="9" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C252" s="23" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="40"/>
       <c r="B253" s="9" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C253" s="23" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="41"/>
       <c r="B254" s="9" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C254" s="23" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A255" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C255" s="22" t="s">
         <v>572</v>
-      </c>
-      <c r="B255" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="C255" s="22" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="36" t="s">
+        <v>574</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="C256" s="22" t="s">
         <v>575</v>
-      </c>
-      <c r="B256" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="C256" s="22" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="37"/>
       <c r="B257" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C257" s="28" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="37"/>
       <c r="B258" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C258" s="22" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="38"/>
       <c r="B259" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C259" s="22" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="36" t="s">
+        <v>583</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="C260" s="22" t="s">
         <v>584</v>
-      </c>
-      <c r="B260" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="C260" s="22" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="210" x14ac:dyDescent="0.25">
       <c r="A261" s="38"/>
       <c r="B261" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C261" s="22" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B262" s="1" t="s">
+      <c r="C262" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="C262" s="1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -8005,10 +8018,10 @@
     </row>
     <row r="270" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A270" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="B270" s="1" t="s">
         <v>594</v>
-      </c>
-      <c r="B270" s="1" t="s">
-        <v>595</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>45</v>
@@ -8035,7 +8048,7 @@
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="47"/>
       <c r="B273" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C273" s="1"/>
     </row>
@@ -8050,101 +8063,101 @@
     </row>
     <row r="275" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A275" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B275" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C275" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="C275" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="42" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="42"/>
       <c r="B277" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C277" s="1"/>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="42"/>
       <c r="B278" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C278" s="1"/>
     </row>
     <row r="279" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A279" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B279" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="B279" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="C279" s="1"/>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B280" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="B280" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="C280" s="1"/>
     </row>
     <row r="281" spans="1:3" ht="180" x14ac:dyDescent="0.25">
       <c r="A281" s="36" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="37"/>
       <c r="B282" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C282" s="35" t="s">
         <v>152</v>
-      </c>
-      <c r="C282" s="35" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" s="37"/>
       <c r="B283" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C283" s="35"/>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="37"/>
       <c r="B284" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C284" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="225" x14ac:dyDescent="0.25">
       <c r="A285" s="38"/>
       <c r="B285" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -8160,58 +8173,58 @@
     </row>
     <row r="287" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="48" t="s">
+        <v>601</v>
+      </c>
+      <c r="B287" s="21" t="s">
         <v>602</v>
       </c>
-      <c r="B287" s="21" t="s">
+      <c r="C287" s="21" t="s">
         <v>603</v>
-      </c>
-      <c r="C287" s="21" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="135" x14ac:dyDescent="0.25">
       <c r="A288" s="49"/>
       <c r="B288" s="21" t="s">
+        <v>604</v>
+      </c>
+      <c r="C288" s="21" t="s">
         <v>605</v>
-      </c>
-      <c r="C288" s="21" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="49"/>
       <c r="B289" s="21" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C289" s="21" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A290" s="49"/>
       <c r="B290" s="21" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C290" s="21" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="291" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A291" s="49"/>
       <c r="B291" s="21" t="s">
+        <v>609</v>
+      </c>
+      <c r="C291" s="21" t="s">
         <v>610</v>
-      </c>
-      <c r="C291" s="21" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="50"/>
       <c r="B292" s="21" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C292" s="21" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>

--- a/KUBERNETES/Kubernetes_liste_des_commandes.xlsx
+++ b/KUBERNETES/Kubernetes_liste_des_commandes.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a5f61b3e4cd8107/Inès_perso/M2i_administraeur_CLOUD.0.0/Cours_Python_M2i/KUBERNETES/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://labom2iformation-my.sharepoint.com/personal/landrine-ines_zounon_labom2iformation_fr/Documents/Documents/.repos/Cours_Python_M2i/KUBERNETES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2412" documentId="8_{4309FA21-DA46-4726-B3AF-5F415FC36ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D317B7D-6E86-4244-8152-AE2A9DCDA1BF}"/>
+  <xr:revisionPtr revIDLastSave="2430" documentId="8_{4309FA21-DA46-4726-B3AF-5F415FC36ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABCE72E2-2031-4C5F-A2F9-A4B8CE44BB7E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8D2D9E53-07E4-4E8B-82A4-55704ED06D6A}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{8D2D9E53-07E4-4E8B-82A4-55704ED06D6A}"/>
   </bookViews>
   <sheets>
     <sheet name="Listes_des_commandes" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Listes_des_commandes!$A$1:$C$286</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Listes_des_commandes!$A$1:$C$294</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="629">
   <si>
     <t>Commandes</t>
   </si>
@@ -1000,9 +1000,6 @@
       </rPr>
       <t xml:space="preserve"> pour sélectionner les Pods portant cette étiquette</t>
     </r>
-  </si>
-  <si>
-    <t>kubectl run nginx-pod --image=nginx</t>
   </si>
   <si>
     <t>kubectl get replicaset</t>
@@ -4788,17 +4785,33 @@
     <t>Cette commande crée un Service nommé storefront à partir du Deployment</t>
   </si>
   <si>
-    <t>²</t>
-  </si>
-  <si>
     <t>kubectl create namespace &lt;nom_donné&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exposer </t>
+  </si>
+  <si>
+    <t>créer un namespace( pour tous les fichiers en fait)</t>
+  </si>
+  <si>
+    <t>kubectl apply -f &lt;namespace&gt;</t>
+  </si>
+  <si>
+    <t>kubectl expose deploy/exo-01 --type=LoadBalancer --port=8080</t>
+  </si>
+  <si>
+    <t>Cette commande crée un Service de type loadbalancer à partir du Deployment</t>
+  </si>
+  <si>
+    <t>kubectl run &lt;nom-du-pod&gt; --image=&lt;image&gt;[:&lt;tag&gt;] --port=&lt;port-conteneur&gt;
+kubectl run nginx-pod --image=nginx</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4840,6 +4853,22 @@
       <b/>
       <sz val="12"/>
       <color rgb="FF002060"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4941,7 +4970,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -5031,7 +5060,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5070,6 +5099,9 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5086,6 +5118,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5431,7 +5475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7416C5AA-AA6E-41AB-BBA6-B527D527C8A0}">
-  <dimension ref="A1:C292"/>
+  <dimension ref="A1:C294"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45" style="5" bestFit="1" customWidth="1"/>
@@ -5453,13 +5497,13 @@
     </row>
     <row r="2" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="B2" s="27" t="s">
         <v>208</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="C2" s="27" t="s">
         <v>209</v>
-      </c>
-      <c r="C2" s="27" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -5476,7 +5520,7 @@
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="38"/>
       <c r="B4" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>177</v>
@@ -5498,2797 +5542,2815 @@
         <v>623</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="53"/>
+      <c r="B7" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A8" s="34"/>
+      <c r="B8" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="75" x14ac:dyDescent="0.25">
-      <c r="A7" s="34"/>
-      <c r="B7" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="43" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B9" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="43"/>
-      <c r="B9" s="9" t="s">
-        <v>172</v>
-      </c>
       <c r="C9" s="9" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="43"/>
       <c r="B10" s="9" t="s">
-        <v>54</v>
+        <v>172</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>53</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="43"/>
       <c r="B11" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="43"/>
       <c r="B12" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="43"/>
       <c r="B13" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="43"/>
       <c r="B14" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="43"/>
       <c r="B15" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>78</v>
+        <v>62</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="43"/>
       <c r="B16" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="43"/>
+      <c r="B17" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C17" s="10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="42" t="s">
-        <v>187</v>
-      </c>
-      <c r="B17" s="2" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="42" t="s">
+        <v>186</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>185</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="42"/>
-      <c r="B18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="42"/>
       <c r="B19" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="35" t="s">
-        <v>72</v>
+        <v>6</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="42"/>
       <c r="B20" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="35"/>
-    </row>
-    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="42"/>
       <c r="B21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>80</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="C21" s="35"/>
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="42"/>
       <c r="B22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="42"/>
+      <c r="B23" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="90" x14ac:dyDescent="0.25">
-      <c r="A23" s="51" t="s">
+    <row r="24" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A24" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B24" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C24" s="9" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="43"/>
-      <c r="B24" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="43"/>
       <c r="B25" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="43"/>
       <c r="B26" s="9" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="43"/>
       <c r="B27" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="43"/>
+      <c r="B28" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C28" s="9" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="42" t="s">
-        <v>188</v>
-      </c>
-      <c r="B28" s="1" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="42" t="s">
+        <v>187</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="42"/>
-      <c r="B29" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="42"/>
       <c r="B30" s="1" t="s">
-        <v>84</v>
+        <v>211</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>83</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="42"/>
       <c r="B31" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="42"/>
+      <c r="B32" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="39" t="s">
-        <v>197</v>
-      </c>
-      <c r="B32" s="9" t="s">
+    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="39" t="s">
+        <v>196</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="9" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="40"/>
-      <c r="B33" s="9" t="s">
-        <v>190</v>
-      </c>
       <c r="C33" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="40"/>
       <c r="B34" s="9" t="s">
-        <v>86</v>
+        <v>189</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="40"/>
       <c r="B35" s="9" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="40"/>
       <c r="B36" s="9" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="40"/>
       <c r="B37" s="9" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="40"/>
       <c r="B38" s="9" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>193</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="40"/>
       <c r="B39" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C39" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="40"/>
       <c r="B40" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>194</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="C40" s="9"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="40"/>
       <c r="B41" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="40"/>
       <c r="B42" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="40"/>
       <c r="B43" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>13</v>
+        <v>92</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="40"/>
       <c r="B44" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="40"/>
       <c r="B45" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C45" s="30" t="s">
-        <v>85</v>
+        <v>15</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A46" s="40"/>
       <c r="B46" s="9" t="s">
-        <v>571</v>
+        <v>19</v>
       </c>
       <c r="C46" s="30" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="40"/>
       <c r="B47" s="9" t="s">
-        <v>589</v>
+        <v>570</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="210" x14ac:dyDescent="0.25">
       <c r="A48" s="40"/>
       <c r="B48" s="9" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C48" s="30" t="s">
-        <v>87</v>
+        <v>589</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="40"/>
       <c r="B49" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="C49" s="30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="40"/>
+      <c r="B50" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="C50" s="30" t="s">
         <v>592</v>
       </c>
-      <c r="C49" s="30" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="41"/>
-      <c r="B50" s="9" t="s">
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="41"/>
+      <c r="B51" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="C50" s="9" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="105" x14ac:dyDescent="0.25">
-      <c r="A51" s="42" t="s">
-        <v>198</v>
-      </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" s="9" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+      <c r="A52" s="42" t="s">
+        <v>197</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>596</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="42"/>
-      <c r="B52" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="42"/>
       <c r="B53" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="42"/>
       <c r="B54" s="1" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="42"/>
       <c r="B55" s="1" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="42"/>
       <c r="B56" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A57" s="42"/>
+      <c r="B57" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="43" t="s">
-        <v>199</v>
-      </c>
-      <c r="B57" s="9" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="43" t="s">
+        <v>198</v>
+      </c>
+      <c r="B58" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="C58" s="9" t="s">
         <v>143</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="43"/>
-      <c r="B58" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="43"/>
       <c r="B59" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="43"/>
       <c r="B60" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="43"/>
+      <c r="B61" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="C61" s="9" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A61" s="42" t="s">
+    <row r="62" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A62" s="42" t="s">
+        <v>199</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C61" s="1" t="s">
+      <c r="C62" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="42"/>
-      <c r="B62" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="42"/>
       <c r="B63" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A64" s="42"/>
       <c r="B64" s="1" t="s">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="42"/>
       <c r="B65" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="42"/>
       <c r="B66" s="1" t="s">
-        <v>148</v>
+        <v>36</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="42"/>
       <c r="B67" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="42"/>
+      <c r="B68" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A69" s="42"/>
+      <c r="B69" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C69" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="43" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="43"/>
+      <c r="B71" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="42" t="s">
         <v>203</v>
       </c>
-      <c r="B68" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="43"/>
-      <c r="B69" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="C69" s="9" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="42" t="s">
+      <c r="B72" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="42"/>
+      <c r="B73" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="43" t="s">
         <v>204</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="42"/>
-      <c r="B71" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="43" t="s">
-        <v>205</v>
-      </c>
-      <c r="B72" s="9" t="s">
+      <c r="B74" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="C74" s="9" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="43"/>
-      <c r="B73" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="43"/>
-      <c r="B74" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="43"/>
       <c r="B75" s="9" t="s">
-        <v>615</v>
+        <v>126</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>616</v>
+        <v>127</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="43"/>
       <c r="B76" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A77" s="43"/>
+      <c r="B77" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="43"/>
+      <c r="B78" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="C78" s="9" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="42" t="s">
-        <v>206</v>
-      </c>
-      <c r="B77" s="1" t="s">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="42" t="s">
+        <v>205</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C79" s="1" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="42"/>
-      <c r="B78" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="42"/>
-      <c r="B79" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="42"/>
       <c r="B80" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="42"/>
+      <c r="B81" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="42"/>
+      <c r="B82" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="B81" s="9" t="s">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="B83" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="C81" s="9" t="s">
+      <c r="C83" s="9" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="43"/>
-      <c r="B82" s="9" t="s">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="43"/>
+      <c r="B84" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="C82" s="9" t="s">
+      <c r="C84" s="9" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A83" s="13" t="s">
+    <row r="85" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A85" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="C85" s="1"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="39" t="s">
         <v>214</v>
       </c>
-      <c r="C83" s="1"/>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="39" t="s">
+      <c r="B86" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="C86" s="44" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="41"/>
+      <c r="B87" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="C84" s="44" t="s">
+      <c r="C87" s="45"/>
+    </row>
+    <row r="88" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="36" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="41"/>
-      <c r="B85" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="C85" s="45"/>
-    </row>
-    <row r="86" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="36" t="s">
+      <c r="B88" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="37"/>
+      <c r="B89" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="37"/>
+      <c r="B90" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A91" s="38"/>
+      <c r="B91" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="37"/>
-      <c r="B87" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="37"/>
-      <c r="B88" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A89" s="38"/>
-      <c r="B89" s="1" t="s">
+      <c r="C91" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A92" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="B92" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="C89" s="6" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A90" s="14" t="s">
+      <c r="C92" s="15" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B90" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="C90" s="15" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="36" t="s">
+      <c r="C93" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="38"/>
+      <c r="B94" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="39" t="s">
+        <v>232</v>
+      </c>
+      <c r="B95" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="38"/>
-      <c r="B92" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="39" t="s">
+      <c r="C95" s="15" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A96" s="41"/>
+      <c r="B96" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="C96" s="15" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="36" t="s">
         <v>233</v>
       </c>
-      <c r="B93" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="C93" s="15" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A94" s="41"/>
-      <c r="B94" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="C94" s="15" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="36" t="s">
+      <c r="B97" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C97" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="C95" s="6" t="s">
+    </row>
+    <row r="98" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A98" s="38"/>
+      <c r="B98" s="1" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A96" s="38"/>
-      <c r="B96" s="1" t="s">
+      <c r="C98" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="C96" s="6" t="s">
+    </row>
+    <row r="99" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="39" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="39" t="s">
+      <c r="B99" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="C99" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="B97" s="9" t="s">
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="40"/>
+      <c r="B100" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="C100" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="C97" s="15" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="40"/>
-      <c r="B98" s="9" t="s">
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="41"/>
+      <c r="B101" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C101" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="C98" s="15" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="41"/>
-      <c r="B99" s="9" t="s">
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="46" t="s">
         <v>245</v>
       </c>
-      <c r="C99" s="15" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="33" t="s">
+      <c r="B102" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C102" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="B100" s="1" t="s">
+    </row>
+    <row r="103" spans="1:3" ht="270" x14ac:dyDescent="0.25">
+      <c r="A103" s="34"/>
+      <c r="B103" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C103" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="C100" s="6" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" ht="270" x14ac:dyDescent="0.25">
-      <c r="A101" s="34"/>
-      <c r="B101" s="1" t="s">
+    </row>
+    <row r="104" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="39" t="s">
+        <v>260</v>
+      </c>
+      <c r="B104" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="C101" s="6" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="39" t="s">
-        <v>261</v>
-      </c>
-      <c r="B102" s="9" t="s">
+      <c r="C104" s="23" t="s">
         <v>251</v>
-      </c>
-      <c r="C102" s="23" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="40"/>
-      <c r="B103" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="C103" s="15" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="40"/>
-      <c r="B104" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="C104" s="15" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="40"/>
       <c r="B105" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="C105" s="15" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="40"/>
+      <c r="B106" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="C106" s="15" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="40"/>
+      <c r="B107" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C107" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="C105" s="15" t="s">
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="41"/>
+      <c r="B108" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="C108" s="15" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="41"/>
-      <c r="B106" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="C106" s="15" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="36" t="s">
+    <row r="109" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="36" t="s">
+        <v>261</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="C109" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="C107" s="6" t="s">
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="37"/>
+      <c r="B110" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C110" s="6" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="37"/>
-      <c r="B108" s="1" t="s">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="38"/>
+      <c r="B111" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="C108" s="6" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="38"/>
-      <c r="B109" s="1" t="s">
+      <c r="C111" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="C109" s="6" t="s">
+    </row>
+    <row r="112" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="39" t="s">
+        <v>278</v>
+      </c>
+      <c r="B112" s="9" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="39" t="s">
-        <v>279</v>
-      </c>
-      <c r="B110" s="9" t="s">
+      <c r="C112" s="15" t="s">
         <v>269</v>
-      </c>
-      <c r="C110" s="15" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="40"/>
-      <c r="B111" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="C111" s="15" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="40"/>
-      <c r="B112" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="C112" s="15" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="40"/>
       <c r="B113" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="C113" s="15" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="40"/>
+      <c r="B114" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="C114" s="15" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="40"/>
+      <c r="B115" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="C115" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="C113" s="15" t="s">
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="41"/>
+      <c r="B116" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="C116" s="15" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="41"/>
-      <c r="B114" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="C114" s="15" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="36" t="s">
+    <row r="117" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="36" t="s">
+        <v>279</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C117" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="B115" s="1" t="s">
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="38"/>
+      <c r="B118" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C118" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="C115" s="6" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="38"/>
-      <c r="B116" s="1" t="s">
+    </row>
+    <row r="119" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A119" s="39" t="s">
         <v>284</v>
       </c>
-      <c r="C116" s="6" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A117" s="39" t="s">
+      <c r="B119" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="C119" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="B117" s="9" t="s">
+    </row>
+    <row r="120" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A120" s="40"/>
+      <c r="B120" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="C120" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="C117" s="15" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A118" s="40"/>
-      <c r="B118" s="9" t="s">
+    </row>
+    <row r="121" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A121" s="41"/>
+      <c r="B121" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="C121" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="C118" s="15" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A119" s="41"/>
-      <c r="B119" s="9" t="s">
+    </row>
+    <row r="122" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="36" t="s">
         <v>291</v>
       </c>
-      <c r="C119" s="15" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="36" t="s">
+      <c r="B122" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C122" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="B120" s="1" t="s">
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="37"/>
+      <c r="B123" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C123" s="19" t="s">
         <v>294</v>
       </c>
-      <c r="C120" s="6" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="37"/>
-      <c r="B121" s="1" t="s">
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="37"/>
+      <c r="B124" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C124" s="19" t="s">
         <v>296</v>
       </c>
-      <c r="C121" s="19" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="37"/>
-      <c r="B122" s="1" t="s">
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="38"/>
+      <c r="B125" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C125" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="C122" s="19" t="s">
+    </row>
+    <row r="126" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="39" t="s">
+        <v>300</v>
+      </c>
+      <c r="B126" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C126" s="23" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="41"/>
+      <c r="B127" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="C127" s="15" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="36" t="s">
+        <v>305</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="38"/>
-      <c r="B123" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="C123" s="7" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="39" t="s">
-        <v>301</v>
-      </c>
-      <c r="B124" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="C124" s="23" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="41"/>
-      <c r="B125" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="C125" s="15" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="36" t="s">
+      <c r="C128" s="19" t="s">
         <v>306</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C126" s="19" t="s">
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="37"/>
+      <c r="B129" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C129" s="19" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="37"/>
-      <c r="B127" s="1" t="s">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="38"/>
+      <c r="B130" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C130" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="C127" s="19" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="38"/>
-      <c r="B128" s="1" t="s">
+    </row>
+    <row r="131" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="39" t="s">
         <v>311</v>
       </c>
-      <c r="C128" s="19" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="39" t="s">
+      <c r="B131" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="C131" s="23" t="s">
         <v>312</v>
       </c>
-      <c r="B129" s="9" t="s">
+    </row>
+    <row r="132" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A132" s="41"/>
+      <c r="B132" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="C129" s="23" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A130" s="41"/>
-      <c r="B130" s="9" t="s">
+      <c r="C132" s="23"/>
+    </row>
+    <row r="133" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A133" s="16" t="s">
         <v>315</v>
       </c>
-      <c r="C130" s="23"/>
-    </row>
-    <row r="131" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A131" s="16" t="s">
+      <c r="B133" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="C133" s="19" t="s">
         <v>316</v>
       </c>
-      <c r="B131" s="17" t="s">
+    </row>
+    <row r="134" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="39" t="s">
         <v>318</v>
       </c>
-      <c r="C131" s="19" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="39" t="s">
+      <c r="B134" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="B132" s="9" t="s">
+      <c r="C134" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="C132" s="23" t="s">
+    </row>
+    <row r="135" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A135" s="40"/>
+      <c r="B135" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="C135" s="23" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A133" s="40"/>
-      <c r="B133" s="8" t="s">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="41"/>
+      <c r="B136" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="C136" s="24" t="s">
         <v>323</v>
       </c>
-      <c r="C133" s="23" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" s="41"/>
-      <c r="B134" s="9" t="s">
+    </row>
+    <row r="137" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="36" t="s">
         <v>325</v>
       </c>
-      <c r="C134" s="24" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="36" t="s">
+      <c r="B137" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C137" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="B135" s="1" t="s">
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="38"/>
+      <c r="B138" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C138" s="20" t="s">
         <v>328</v>
       </c>
-      <c r="C135" s="19" t="s">
+    </row>
+    <row r="139" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="39" t="s">
+        <v>337</v>
+      </c>
+      <c r="B139" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="C139" s="9" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A140" s="41"/>
+      <c r="B140" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="C140" s="23" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="36" t="s">
+        <v>338</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C141" s="19" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="38"/>
+      <c r="B142" s="1" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="38"/>
-      <c r="B136" s="1" t="s">
+      <c r="C142" s="19" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A143" s="39" t="s">
+        <v>343</v>
+      </c>
+      <c r="B143" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="C143" s="23" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="41"/>
+      <c r="B144" s="25" t="s">
+        <v>342</v>
+      </c>
+      <c r="C144" s="23" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A145" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C145" s="19" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="39" t="s">
+        <v>352</v>
+      </c>
+      <c r="B146" s="25" t="s">
         <v>330</v>
       </c>
-      <c r="C136" s="20" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="39" t="s">
-        <v>338</v>
-      </c>
-      <c r="B137" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="C137" s="9" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A138" s="41"/>
-      <c r="B138" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="C138" s="23" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="36" t="s">
-        <v>339</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C139" s="19" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="38"/>
-      <c r="B140" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C140" s="19" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A141" s="39" t="s">
-        <v>344</v>
-      </c>
-      <c r="B141" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="C141" s="23" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="41"/>
-      <c r="B142" s="25" t="s">
-        <v>343</v>
-      </c>
-      <c r="C142" s="23" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A143" s="16" t="s">
-        <v>345</v>
-      </c>
-      <c r="B143" s="1" t="s">
+      <c r="C146" s="23" t="s">
         <v>347</v>
       </c>
-      <c r="C143" s="19" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" s="39" t="s">
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="40"/>
+      <c r="B147" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="C147" s="23" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="41"/>
+      <c r="B148" s="25" t="s">
+        <v>351</v>
+      </c>
+      <c r="C148" s="23" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="36" t="s">
         <v>353</v>
       </c>
-      <c r="B144" s="25" t="s">
-        <v>331</v>
-      </c>
-      <c r="C144" s="23" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" s="40"/>
-      <c r="B145" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="C145" s="23" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="41"/>
-      <c r="B146" s="25" t="s">
-        <v>352</v>
-      </c>
-      <c r="C146" s="23" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="36" t="s">
-        <v>354</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="C147" s="19" t="s">
+      <c r="B149" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="C149" s="19" t="s">
         <v>155</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" s="37"/>
-      <c r="B148" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C148" s="19" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="37"/>
-      <c r="B149" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C149" s="19" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="37"/>
       <c r="B150" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C150" s="19" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="37"/>
+      <c r="B151" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C151" s="19" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="37"/>
+      <c r="B152" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C150" s="19" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" s="38"/>
-      <c r="B151" s="1" t="s">
+      <c r="C152" s="19" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="38"/>
+      <c r="B153" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C151" s="19"/>
-    </row>
-    <row r="152" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="39" t="s">
+      <c r="C153" s="19"/>
+    </row>
+    <row r="154" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="39" t="s">
+        <v>358</v>
+      </c>
+      <c r="B154" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="C154" s="23" t="s">
         <v>359</v>
-      </c>
-      <c r="B152" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="C152" s="23" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" s="40"/>
-      <c r="B153" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="C153" s="29" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" s="40"/>
-      <c r="B154" s="29" t="s">
-        <v>365</v>
-      </c>
-      <c r="C154" s="23" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="40"/>
       <c r="B155" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="C155" s="23" t="s">
-        <v>366</v>
+        <v>361</v>
+      </c>
+      <c r="C155" s="29" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="40"/>
-      <c r="B156" s="9" t="s">
-        <v>369</v>
+      <c r="B156" s="29" t="s">
+        <v>364</v>
       </c>
       <c r="C156" s="23" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="40"/>
       <c r="B157" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="C157" s="23" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="40"/>
+      <c r="B158" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="C158" s="23" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="40"/>
+      <c r="B159" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="C159" s="23" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A160" s="41"/>
+      <c r="B160" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="C160" s="23" t="s">
         <v>371</v>
       </c>
-      <c r="C157" s="23" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" ht="90" x14ac:dyDescent="0.25">
-      <c r="A158" s="41"/>
-      <c r="B158" s="9" t="s">
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="49" t="s">
         <v>373</v>
       </c>
-      <c r="C158" s="23" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" s="48" t="s">
+      <c r="B161" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="C161" s="21" t="s">
         <v>374</v>
       </c>
-      <c r="B159" s="21" t="s">
-        <v>387</v>
-      </c>
-      <c r="C159" s="21" t="s">
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="50"/>
+      <c r="B162" s="1" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" s="49"/>
-      <c r="B160" s="1" t="s">
+      <c r="C162" s="21" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="50"/>
+      <c r="B163" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C160" s="21" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" s="49"/>
-      <c r="B161" s="1" t="s">
+      <c r="C163" s="21" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="50"/>
+      <c r="B164" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="C161" s="21" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" s="49"/>
-      <c r="B162" s="1" t="s">
+      <c r="C164" s="21" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="50"/>
+      <c r="B165" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C165" s="19" t="s">
         <v>378</v>
       </c>
-      <c r="C162" s="21" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" s="49"/>
-      <c r="B163" s="1" t="s">
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="50"/>
+      <c r="B166" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="C163" s="19" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" s="49"/>
-      <c r="B164" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="C164" s="19" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" s="49"/>
-      <c r="B165" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="C165" s="20" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" s="49"/>
-      <c r="B166" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="C166" s="20" t="s">
-        <v>382</v>
+      <c r="C166" s="19" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="50"/>
       <c r="B167" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="C167" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="C167" s="20" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="50"/>
+      <c r="B168" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C168" s="20" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="51"/>
+      <c r="B169" s="1" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="39" t="s">
+      <c r="C169" s="19" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="39" t="s">
+        <v>387</v>
+      </c>
+      <c r="B170" s="25" t="s">
+        <v>389</v>
+      </c>
+      <c r="C170" s="23" t="s">
         <v>388</v>
       </c>
-      <c r="B168" s="25" t="s">
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="40"/>
+      <c r="B171" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="C168" s="23" t="s">
+      <c r="C171" s="23" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="40"/>
+      <c r="B172" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="C172" s="23" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="41"/>
+      <c r="B173" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="C173" s="23" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="36" t="s">
+        <v>394</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C174" s="19" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="37"/>
+      <c r="B175" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C175" s="19" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A176" s="37"/>
+      <c r="B176" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C176" s="19" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="38"/>
+      <c r="B177" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C177" s="19" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="39" t="s">
+        <v>403</v>
+      </c>
+      <c r="B178" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="C178" s="23" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A179" s="40"/>
+      <c r="B179" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="C179" s="23" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="41"/>
+      <c r="B180" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="C180" s="23" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C181" s="19" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A182" s="37"/>
+      <c r="B182" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="C182" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="37"/>
+      <c r="B183" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C183" s="19" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A184" s="38"/>
+      <c r="B184" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C184" s="19" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="39" t="s">
+        <v>418</v>
+      </c>
+      <c r="B185" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="C185" s="23" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A186" s="40"/>
+      <c r="B186" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="C186" s="23" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="40"/>
+      <c r="B187" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="C187" s="29" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A188" s="41"/>
+      <c r="B188" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="C188" s="23" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A189" s="36" t="s">
+        <v>427</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C189" s="19" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A190" s="37"/>
+      <c r="B190" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C190" s="19" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A191" s="38"/>
+      <c r="B191" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C191" s="19" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="39" t="s">
+        <v>434</v>
+      </c>
+      <c r="B192" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="C192" s="23" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A193" s="40"/>
+      <c r="B193" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="C193" s="9" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="41"/>
+      <c r="B194" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="C194" s="23" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="36" t="s">
+        <v>441</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C195" s="19" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="37"/>
+      <c r="B196" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C196" s="19" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="37"/>
+      <c r="B197" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C197" s="19" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A198" s="38"/>
+      <c r="B198" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C198" s="19" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="39" t="s">
+        <v>450</v>
+      </c>
+      <c r="B199" s="9" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" s="40"/>
-      <c r="B169" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="C169" s="23" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" s="40"/>
-      <c r="B170" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="C170" s="23" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" s="41"/>
-      <c r="B171" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="C171" s="23" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="36" t="s">
-        <v>395</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="C172" s="19" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" s="37"/>
-      <c r="B173" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="C173" s="19" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A174" s="37"/>
-      <c r="B174" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="C174" s="19" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" s="38"/>
-      <c r="B175" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="C175" s="19" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" s="39" t="s">
-        <v>404</v>
-      </c>
-      <c r="B176" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="C176" s="23" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A177" s="40"/>
-      <c r="B177" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="C177" s="23" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" s="41"/>
-      <c r="B178" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="C178" s="23" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="36" t="s">
-        <v>410</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="C179" s="19" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A180" s="37"/>
-      <c r="B180" s="8" t="s">
-        <v>414</v>
-      </c>
-      <c r="C180" s="19" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" s="37"/>
-      <c r="B181" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C181" s="19" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A182" s="38"/>
-      <c r="B182" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="C182" s="19" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="39" t="s">
-        <v>419</v>
-      </c>
-      <c r="B183" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="C183" s="23" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A184" s="40"/>
-      <c r="B184" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="C184" s="23" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" s="40"/>
-      <c r="B185" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="C185" s="29" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A186" s="41"/>
-      <c r="B186" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="C186" s="23" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A187" s="36" t="s">
-        <v>428</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C187" s="19" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A188" s="37"/>
-      <c r="B188" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="C188" s="19" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A189" s="38"/>
-      <c r="B189" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="C189" s="19" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="39" t="s">
-        <v>435</v>
-      </c>
-      <c r="B190" s="9" t="s">
-        <v>437</v>
-      </c>
-      <c r="C190" s="23" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A191" s="40"/>
-      <c r="B191" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="C191" s="9" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" s="41"/>
-      <c r="B192" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="C192" s="23" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" s="36" t="s">
-        <v>442</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="C193" s="19" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" s="37"/>
-      <c r="B194" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="C194" s="19" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="37"/>
-      <c r="B195" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="C195" s="19" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A196" s="38"/>
-      <c r="B196" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="C196" s="19" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" s="39" t="s">
+      <c r="C199" s="23" t="s">
         <v>451</v>
-      </c>
-      <c r="B197" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="C197" s="23" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" s="40"/>
-      <c r="B198" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="C198" s="23" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" s="40"/>
-      <c r="B199" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="C199" s="23" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="40"/>
       <c r="B200" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="C200" s="23" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="40"/>
+      <c r="B201" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="C201" s="23" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="40"/>
+      <c r="B202" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="C202" s="23" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="41"/>
+      <c r="B203" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="C203" s="23" t="s">
         <v>456</v>
       </c>
-      <c r="C200" s="23" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" s="41"/>
-      <c r="B201" s="9" t="s">
+    </row>
+    <row r="204" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="36" t="s">
         <v>458</v>
       </c>
-      <c r="C201" s="23" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="36" t="s">
+      <c r="B204" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C204" s="22" t="s">
         <v>459</v>
       </c>
-      <c r="B202" s="1" t="s">
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="37"/>
+      <c r="B205" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C205" s="22" t="s">
         <v>461</v>
       </c>
-      <c r="C202" s="22" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" s="37"/>
-      <c r="B203" s="1" t="s">
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="37"/>
+      <c r="B206" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C206" s="22" t="s">
         <v>463</v>
       </c>
-      <c r="C203" s="22" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" s="37"/>
-      <c r="B204" s="1" t="s">
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="38"/>
+      <c r="B207" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C207" s="22" t="s">
         <v>465</v>
       </c>
-      <c r="C204" s="22" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" s="38"/>
-      <c r="B205" s="1" t="s">
+    </row>
+    <row r="208" spans="1:3" ht="270" x14ac:dyDescent="0.25">
+      <c r="A208" s="14" t="s">
         <v>467</v>
       </c>
-      <c r="C205" s="22" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" ht="270" x14ac:dyDescent="0.25">
-      <c r="A206" s="14" t="s">
+      <c r="B208" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="C208" s="23"/>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="36" t="s">
         <v>468</v>
       </c>
-      <c r="B206" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="C206" s="23"/>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" s="36" t="s">
+      <c r="B209" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C209" s="19" t="s">
         <v>469</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="C207" s="19" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" s="37"/>
-      <c r="B208" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="C208" s="19" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" s="37"/>
-      <c r="B209" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="C209" s="19" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="37"/>
       <c r="B210" s="1" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C210" s="19" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="37"/>
       <c r="B211" s="1" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C211" s="19" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="37"/>
       <c r="B212" s="1" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C212" s="19" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="37"/>
       <c r="B213" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C213" s="19" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="37"/>
+      <c r="B214" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C214" s="19" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="37"/>
+      <c r="B215" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C215" s="19" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="38"/>
+      <c r="B216" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="C213" s="19" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A214" s="38"/>
-      <c r="B214" s="1" t="s">
+      <c r="C216" s="19" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A217" s="39" t="s">
         <v>481</v>
       </c>
-      <c r="C214" s="19" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="39" t="s">
+      <c r="B217" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="C217" s="23" t="s">
         <v>482</v>
       </c>
-      <c r="B215" s="9" t="s">
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="40"/>
+      <c r="B218" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="C218" s="23" t="s">
         <v>484</v>
       </c>
-      <c r="C215" s="23" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A216" s="40"/>
-      <c r="B216" s="9" t="s">
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="40"/>
+      <c r="B219" s="9" t="s">
         <v>486</v>
       </c>
-      <c r="C216" s="23" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" s="40"/>
-      <c r="B217" s="9" t="s">
+      <c r="C219" s="23" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="41"/>
+      <c r="B220" s="9" t="s">
         <v>487</v>
       </c>
-      <c r="C217" s="23" t="s">
+      <c r="C220" s="23" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218" s="41"/>
-      <c r="B218" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="C218" s="23" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="36" t="s">
+    <row r="221" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A221" s="36" t="s">
+        <v>526</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C221" s="22" t="s">
         <v>527</v>
       </c>
-      <c r="B219" s="1" t="s">
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="37"/>
+      <c r="B222" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C222" s="28" t="s">
         <v>529</v>
       </c>
-      <c r="C219" s="22" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220" s="37"/>
-      <c r="B220" s="1" t="s">
+    </row>
+    <row r="223" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A223" s="38"/>
+      <c r="B223" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C223" s="22" t="s">
         <v>531</v>
       </c>
-      <c r="C220" s="28" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A221" s="38"/>
-      <c r="B221" s="1" t="s">
+    </row>
+    <row r="224" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A224" s="39" t="s">
         <v>533</v>
       </c>
-      <c r="C221" s="22" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="39" t="s">
+      <c r="B224" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="C224" s="23" t="s">
         <v>534</v>
       </c>
-      <c r="B222" s="9" t="s">
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="40"/>
+      <c r="B225" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="C225" s="23" t="s">
         <v>536</v>
       </c>
-      <c r="C222" s="23" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" s="40"/>
-      <c r="B223" s="9" t="s">
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="40"/>
+      <c r="B226" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="C226" s="23" t="s">
         <v>538</v>
       </c>
-      <c r="C223" s="23" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" s="40"/>
-      <c r="B224" s="9" t="s">
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="41"/>
+      <c r="B227" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="C227" s="23" t="s">
         <v>540</v>
       </c>
-      <c r="C224" s="23" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" s="41"/>
-      <c r="B225" s="9" t="s">
+    </row>
+    <row r="228" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="36" t="s">
         <v>542</v>
       </c>
-      <c r="C225" s="23" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A226" s="36" t="s">
+      <c r="B228" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="B226" s="1" t="s">
+      <c r="C228" s="22" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="37"/>
+      <c r="B229" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C229" s="22" t="s">
         <v>544</v>
       </c>
-      <c r="C226" s="22" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" s="37"/>
-      <c r="B227" s="1" t="s">
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="38"/>
+      <c r="B230" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C230" s="22" t="s">
         <v>546</v>
       </c>
-      <c r="C227" s="22" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228" s="38"/>
-      <c r="B228" s="1" t="s">
+    </row>
+    <row r="231" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A231" s="39" t="s">
         <v>548</v>
       </c>
-      <c r="C228" s="22" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A229" s="39" t="s">
+      <c r="B231" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="C231" s="23" t="s">
         <v>549</v>
       </c>
-      <c r="B229" s="9" t="s">
+    </row>
+    <row r="232" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A232" s="40"/>
+      <c r="B232" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="C232" s="23" t="s">
         <v>551</v>
       </c>
-      <c r="C229" s="23" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A230" s="40"/>
-      <c r="B230" s="9" t="s">
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="41"/>
+      <c r="B233" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="C233" s="23" t="s">
         <v>553</v>
       </c>
-      <c r="C230" s="23" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A231" s="41"/>
-      <c r="B231" s="9" t="s">
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="36" t="s">
+        <v>489</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C234" s="19" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="37"/>
+      <c r="B235" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C235" s="19" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="37"/>
+      <c r="B236" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C236" s="19" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="38"/>
+      <c r="B237" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C237" s="19" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A238" s="14" t="s">
+        <v>497</v>
+      </c>
+      <c r="B238" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="C238" s="23" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A239" s="36" t="s">
+        <v>500</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C239" s="19" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A240" s="37"/>
+      <c r="B240" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C240" s="19" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A241" s="38"/>
+      <c r="B241" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C241" s="19" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A242" s="39" t="s">
+        <v>507</v>
+      </c>
+      <c r="B242" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="C242" s="23" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A243" s="41"/>
+      <c r="B243" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="C243" s="23" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="36" t="s">
+        <v>512</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C244" s="19" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A245" s="38"/>
+      <c r="B245" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C245" s="19" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="39" t="s">
+        <v>517</v>
+      </c>
+      <c r="B246" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="C246" s="23" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="40"/>
+      <c r="B247" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="C247" s="23" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="40"/>
+      <c r="B248" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="C248" s="23" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="41"/>
+      <c r="B249" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="C249" s="23" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="36" t="s">
         <v>555</v>
       </c>
-      <c r="C231" s="23" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A232" s="36" t="s">
-        <v>490</v>
-      </c>
-      <c r="B232" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="C232" s="19" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A233" s="37"/>
-      <c r="B233" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="C233" s="19" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A234" s="37"/>
-      <c r="B234" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="C234" s="19" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A235" s="38"/>
-      <c r="B235" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="C235" s="19" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A236" s="14" t="s">
-        <v>498</v>
-      </c>
-      <c r="B236" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="C236" s="23" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="36" t="s">
-        <v>501</v>
-      </c>
-      <c r="B237" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="C237" s="19" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A238" s="37"/>
-      <c r="B238" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="C238" s="19" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A239" s="38"/>
-      <c r="B239" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C239" s="19" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A240" s="39" t="s">
-        <v>508</v>
-      </c>
-      <c r="B240" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="C240" s="23" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A241" s="41"/>
-      <c r="B241" s="9" t="s">
-        <v>512</v>
-      </c>
-      <c r="C241" s="23" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A242" s="36" t="s">
-        <v>513</v>
-      </c>
-      <c r="B242" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="C242" s="19" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A243" s="38"/>
-      <c r="B243" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="C243" s="19" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A244" s="39" t="s">
-        <v>518</v>
-      </c>
-      <c r="B244" s="9" t="s">
-        <v>520</v>
-      </c>
-      <c r="C244" s="23" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A245" s="40"/>
-      <c r="B245" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="C245" s="23" t="s">
+      <c r="B250" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="C250" s="19" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A251" s="37"/>
+      <c r="B251" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C251" s="19" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="38"/>
+      <c r="B252" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="C252" s="19" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A253" s="39" t="s">
+        <v>562</v>
+      </c>
+      <c r="B253" s="9" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A246" s="40"/>
-      <c r="B246" s="9" t="s">
-        <v>524</v>
-      </c>
-      <c r="C246" s="23" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A247" s="41"/>
-      <c r="B247" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="C247" s="23" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A248" s="36" t="s">
-        <v>556</v>
-      </c>
-      <c r="B248" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="C248" s="19" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A249" s="37"/>
-      <c r="B249" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="C249" s="19" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A250" s="38"/>
-      <c r="B250" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="C250" s="19" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A251" s="39" t="s">
+      <c r="C253" s="23" t="s">
         <v>563</v>
       </c>
-      <c r="B251" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="C251" s="23" t="s">
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="40"/>
+      <c r="B254" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="C254" s="23" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A252" s="40"/>
-      <c r="B252" s="9" t="s">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="40"/>
+      <c r="B255" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="C255" s="23" t="s">
         <v>566</v>
       </c>
-      <c r="C252" s="23" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A253" s="40"/>
-      <c r="B253" s="9" t="s">
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="41"/>
+      <c r="B256" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="C256" s="23" t="s">
         <v>568</v>
       </c>
-      <c r="C253" s="23" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A254" s="41"/>
-      <c r="B254" s="9" t="s">
-        <v>570</v>
-      </c>
-      <c r="C254" s="23" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A255" s="16" t="s">
+    </row>
+    <row r="257" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A257" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C257" s="22" t="s">
         <v>572</v>
       </c>
-      <c r="B255" s="1" t="s">
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="36" t="s">
         <v>574</v>
       </c>
-      <c r="C255" s="22" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A256" s="36" t="s">
+      <c r="B258" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="C258" s="22" t="s">
         <v>575</v>
       </c>
-      <c r="B256" s="1" t="s">
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="37"/>
+      <c r="B259" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="C259" s="28" t="s">
         <v>577</v>
       </c>
-      <c r="C256" s="22" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A257" s="37"/>
-      <c r="B257" s="1" t="s">
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="37"/>
+      <c r="B260" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="C260" s="22" t="s">
         <v>579</v>
       </c>
-      <c r="C257" s="28" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A258" s="37"/>
-      <c r="B258" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="C258" s="22" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A259" s="38"/>
-      <c r="B259" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="C259" s="22" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A260" s="36" t="s">
-        <v>584</v>
-      </c>
-      <c r="B260" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="C260" s="22" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="38"/>
       <c r="B261" s="1" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="C261" s="22" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A262" s="36" t="s">
+        <v>583</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="C262" s="22" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A263" s="38"/>
+      <c r="B263" s="1" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A262" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C262" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A263" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B263" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C263" s="1"/>
+      <c r="C263" s="22" t="s">
+        <v>586</v>
+      </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
-        <v>29</v>
+        <v>178</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C264" s="1"/>
-    </row>
-    <row r="265" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B265" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C265" s="12" t="s">
-        <v>32</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C265" s="1"/>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C266" s="1"/>
     </row>
-    <row r="267" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A267" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B267" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C267" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
+      </c>
+      <c r="B267" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C267" s="12" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C268" s="1"/>
+    </row>
+    <row r="269" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A269" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B268" s="1" t="s">
+      <c r="B270" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C268" s="1"/>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A269" s="4" t="s">
+      <c r="C270" s="1"/>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B269" s="1" t="s">
+      <c r="B271" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C269" s="1"/>
-    </row>
-    <row r="270" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A270" s="4" t="s">
+      <c r="C271" s="1"/>
+    </row>
+    <row r="272" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A272" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="B272" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="B270" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="C270" s="1" t="s">
+      <c r="C272" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A271" s="31" t="s">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B271" s="8" t="s">
+      <c r="B273" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C271" s="1"/>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A272" s="46" t="s">
+      <c r="C273" s="1"/>
+    </row>
+    <row r="274" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A274" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="B272" s="8" t="s">
+      <c r="B274" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C272" s="1"/>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A273" s="47"/>
-      <c r="B273" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="C273" s="1"/>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A274" s="4" t="s">
+      <c r="C274" s="1"/>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="48"/>
+      <c r="B275" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C275" s="1"/>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B274" s="1" t="s">
+      <c r="B276" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C274" s="1"/>
-    </row>
-    <row r="275" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A275" s="4" t="s">
+      <c r="C276" s="1"/>
+    </row>
+    <row r="277" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A277" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B275" s="1" t="s">
+      <c r="B277" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C275" s="1" t="s">
+      <c r="C277" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A276" s="42" t="s">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" s="42" t="s">
         <v>166</v>
       </c>
-      <c r="B276" s="1" t="s">
+      <c r="B278" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C276" s="1" t="s">
+      <c r="C278" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A277" s="42"/>
-      <c r="B277" s="1" t="s">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" s="42"/>
+      <c r="B279" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C277" s="1"/>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A278" s="42"/>
-      <c r="B278" s="1" t="s">
+      <c r="C279" s="1"/>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" s="42"/>
+      <c r="B280" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C278" s="1"/>
-    </row>
-    <row r="279" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A279" s="4" t="s">
+      <c r="C280" s="1"/>
+    </row>
+    <row r="281" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A281" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B279" s="1" t="s">
+      <c r="B281" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C279" s="1"/>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A280" s="4" t="s">
+      <c r="C281" s="1"/>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B280" s="1" t="s">
+      <c r="B282" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C280" s="1"/>
-    </row>
-    <row r="281" spans="1:3" ht="180" x14ac:dyDescent="0.25">
-      <c r="A281" s="36" t="s">
+      <c r="C282" s="1"/>
+    </row>
+    <row r="283" spans="1:3" ht="180" x14ac:dyDescent="0.25">
+      <c r="A283" s="54" t="s">
+        <v>599</v>
+      </c>
+      <c r="B283" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" s="55"/>
+      <c r="B284" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C284" s="35" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" s="55"/>
+      <c r="B285" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C285" s="35"/>
+    </row>
+    <row r="286" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A286" s="55"/>
+      <c r="B286" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C286" s="7" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" ht="225" x14ac:dyDescent="0.25">
+      <c r="A287" s="56"/>
+      <c r="B287" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="C287" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="B281" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C281" s="1" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A282" s="37"/>
-      <c r="B282" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C282" s="35" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A283" s="37"/>
-      <c r="B283" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C283" s="35"/>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A284" s="37"/>
-      <c r="B284" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C284" s="7" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3" ht="225" x14ac:dyDescent="0.25">
-      <c r="A285" s="38"/>
-      <c r="B285" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="C285" s="1" t="s">
+    </row>
+    <row r="288" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A288" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B288" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C288" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A289" s="49" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="286" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A286" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B286" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C286" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="48" t="s">
+      <c r="B289" s="21" t="s">
         <v>602</v>
       </c>
-      <c r="B287" s="21" t="s">
+      <c r="C289" s="21" t="s">
         <v>603</v>
       </c>
-      <c r="C287" s="21" t="s">
+    </row>
+    <row r="290" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+      <c r="A290" s="50"/>
+      <c r="B290" s="21" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="288" spans="1:3" ht="135" x14ac:dyDescent="0.25">
-      <c r="A288" s="49"/>
-      <c r="B288" s="21" t="s">
+      <c r="C290" s="21" t="s">
         <v>605</v>
       </c>
-      <c r="C288" s="21" t="s">
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" s="50"/>
+      <c r="B291" s="21" t="s">
+        <v>607</v>
+      </c>
+      <c r="C291" s="21" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A289" s="49"/>
-      <c r="B289" s="21" t="s">
-        <v>608</v>
-      </c>
-      <c r="C289" s="21" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A290" s="49"/>
-      <c r="B290" s="21" t="s">
-        <v>609</v>
-      </c>
-      <c r="C290" s="21" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A291" s="49"/>
-      <c r="B291" s="21" t="s">
-        <v>610</v>
-      </c>
-      <c r="C291" s="21" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A292" s="50"/>
       <c r="B292" s="21" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="C292" s="21" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A293" s="50"/>
+      <c r="B293" s="21" t="s">
+        <v>609</v>
+      </c>
+      <c r="C293" s="21" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" s="51"/>
+      <c r="B294" s="21" t="s">
         <v>613</v>
       </c>
+      <c r="C294" s="21" t="s">
+        <v>612</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C286" xr:uid="{7416C5AA-AA6E-41AB-BBA6-B527D527C8A0}"/>
+  <autoFilter ref="A1:C294" xr:uid="{7416C5AA-AA6E-41AB-BBA6-B527D527C8A0}"/>
   <mergeCells count="72">
-    <mergeCell ref="A287:A292"/>
-    <mergeCell ref="A8:A16"/>
-    <mergeCell ref="A23:A27"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="A28:A31"/>
-    <mergeCell ref="A32:A50"/>
-    <mergeCell ref="A159:A167"/>
-    <mergeCell ref="A168:A171"/>
-    <mergeCell ref="A172:A175"/>
-    <mergeCell ref="A276:A278"/>
-    <mergeCell ref="A248:A250"/>
-    <mergeCell ref="A232:A235"/>
-    <mergeCell ref="A237:A239"/>
-    <mergeCell ref="A240:A241"/>
+    <mergeCell ref="A289:A294"/>
+    <mergeCell ref="A9:A17"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="A33:A51"/>
+    <mergeCell ref="A161:A169"/>
+    <mergeCell ref="A170:A173"/>
+    <mergeCell ref="A174:A177"/>
+    <mergeCell ref="A278:A280"/>
+    <mergeCell ref="A250:A252"/>
+    <mergeCell ref="A234:A237"/>
+    <mergeCell ref="A239:A241"/>
     <mergeCell ref="A242:A243"/>
-    <mergeCell ref="A244:A247"/>
-    <mergeCell ref="A193:A196"/>
-    <mergeCell ref="A197:A201"/>
-    <mergeCell ref="A202:A205"/>
-    <mergeCell ref="A207:A214"/>
-    <mergeCell ref="A272:A273"/>
-    <mergeCell ref="A256:A259"/>
-    <mergeCell ref="A260:A261"/>
-    <mergeCell ref="A147:A151"/>
-    <mergeCell ref="A215:A218"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="A179:A182"/>
-    <mergeCell ref="A183:A186"/>
-    <mergeCell ref="A187:A189"/>
-    <mergeCell ref="A190:A192"/>
-    <mergeCell ref="A251:A254"/>
-    <mergeCell ref="A219:A221"/>
-    <mergeCell ref="A222:A225"/>
-    <mergeCell ref="A226:A228"/>
-    <mergeCell ref="A229:A231"/>
-    <mergeCell ref="A152:A158"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A244:A245"/>
+    <mergeCell ref="A246:A249"/>
+    <mergeCell ref="A195:A198"/>
+    <mergeCell ref="A199:A203"/>
+    <mergeCell ref="A204:A207"/>
+    <mergeCell ref="A209:A216"/>
+    <mergeCell ref="A274:A275"/>
+    <mergeCell ref="A258:A261"/>
+    <mergeCell ref="A262:A263"/>
+    <mergeCell ref="A149:A153"/>
+    <mergeCell ref="A217:A220"/>
+    <mergeCell ref="A178:A180"/>
+    <mergeCell ref="A181:A184"/>
+    <mergeCell ref="A185:A188"/>
+    <mergeCell ref="A189:A191"/>
+    <mergeCell ref="A192:A194"/>
+    <mergeCell ref="A253:A256"/>
+    <mergeCell ref="A221:A223"/>
+    <mergeCell ref="A224:A227"/>
+    <mergeCell ref="A228:A230"/>
+    <mergeCell ref="A231:A233"/>
+    <mergeCell ref="A154:A160"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="A88:A91"/>
     <mergeCell ref="A93:A94"/>
-    <mergeCell ref="A102:A106"/>
     <mergeCell ref="A95:A96"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="A126:A128"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A129:A130"/>
-    <mergeCell ref="A115:A116"/>
-    <mergeCell ref="A117:A119"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A110:A114"/>
-    <mergeCell ref="A72:A76"/>
-    <mergeCell ref="A77:A80"/>
-    <mergeCell ref="A97:A99"/>
-    <mergeCell ref="A120:A123"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C282:C283"/>
-    <mergeCell ref="A281:A285"/>
+    <mergeCell ref="A104:A108"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A128:A130"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A131:A132"/>
+    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="A119:A121"/>
+    <mergeCell ref="A109:A111"/>
+    <mergeCell ref="A112:A116"/>
+    <mergeCell ref="A74:A78"/>
+    <mergeCell ref="A79:A82"/>
+    <mergeCell ref="A99:A101"/>
+    <mergeCell ref="A122:A125"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="C284:C285"/>
+    <mergeCell ref="A283:A287"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A144:A146"/>
-    <mergeCell ref="A132:A134"/>
-    <mergeCell ref="A135:A136"/>
+    <mergeCell ref="A146:A148"/>
+    <mergeCell ref="A134:A136"/>
     <mergeCell ref="A137:A138"/>
     <mergeCell ref="A139:A140"/>
     <mergeCell ref="A141:A142"/>
-    <mergeCell ref="A17:A22"/>
-    <mergeCell ref="A51:A56"/>
-    <mergeCell ref="A57:A60"/>
-    <mergeCell ref="A61:A67"/>
-    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A143:A144"/>
+    <mergeCell ref="A18:A23"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A62:A69"/>
     <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
